--- a/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
+++ b/docs/oc-mensuales/mobiliario-general-escolar-y-clinico/dic-2025.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M91"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>12341737.8</v>
+        <v>13471.12</v>
       </c>
     </row>
     <row r="3">
@@ -626,11 +626,11 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19681750</v>
+        <v>21482.8</v>
       </c>
     </row>
     <row r="4">
@@ -687,11 +687,11 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>11121741.7</v>
+        <v>12139.48</v>
       </c>
     </row>
     <row r="5">
@@ -748,11 +748,11 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>20249550</v>
+        <v>22102.56</v>
       </c>
     </row>
     <row r="6">
@@ -809,11 +809,11 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>7330372.8</v>
+        <v>8001.17</v>
       </c>
     </row>
     <row r="7">
@@ -870,11 +870,11 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>7426900.6</v>
+        <v>8106.53</v>
       </c>
     </row>
     <row r="8">
@@ -931,11 +931,11 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>9875460</v>
+        <v>10779.15</v>
       </c>
     </row>
     <row r="9">
@@ -992,11 +992,11 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>12757314.64</v>
+        <v>13924.72</v>
       </c>
     </row>
     <row r="10">
@@ -1053,11 +1053,11 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>8187485.6</v>
+        <v>8936.709999999999</v>
       </c>
     </row>
     <row r="11">
@@ -1114,11 +1114,11 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>7535270.4</v>
+        <v>8224.809999999999</v>
       </c>
     </row>
     <row r="12">
@@ -1175,11 +1175,11 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>8466255</v>
+        <v>9240.99</v>
       </c>
     </row>
     <row r="13">
@@ -1236,11 +1236,11 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>12736174.75</v>
+        <v>13901.65</v>
       </c>
     </row>
     <row r="14">
@@ -1297,11 +1297,11 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>7886187.4</v>
+        <v>8607.84</v>
       </c>
     </row>
     <row r="15">
@@ -1358,11 +1358,11 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>7415924.45</v>
+        <v>8094.55</v>
       </c>
     </row>
     <row r="16">
@@ -1419,11 +1419,11 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>24111477.4</v>
+        <v>26317.89</v>
       </c>
     </row>
     <row r="17">
@@ -1480,11 +1480,11 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>11730000</v>
+        <v>12803.4</v>
       </c>
     </row>
     <row r="18">
@@ -1541,11 +1541,11 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13876585.8</v>
+        <v>15146.42</v>
       </c>
     </row>
     <row r="19">
@@ -1602,11 +1602,11 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>16099876.72</v>
+        <v>17573.16</v>
       </c>
     </row>
     <row r="20">
@@ -1663,11 +1663,11 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>16422183.4</v>
+        <v>17924.96</v>
       </c>
     </row>
     <row r="21">
@@ -1724,11 +1724,11 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>12500208.7</v>
+        <v>13644.09</v>
       </c>
     </row>
     <row r="22">
@@ -1785,11 +1785,11 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>9224595.939999999</v>
+        <v>10068.73</v>
       </c>
     </row>
     <row r="23">
@@ -1846,17 +1846,17 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10299809.8</v>
+        <v>11242.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>707420-195-CM25</t>
+          <t>622-791-CM25</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1876,48 +1876,48 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.805.000-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>76.404.809-1</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14454522</v>
+        <v>52239.59</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>622-791-CM25</t>
+          <t>707420-195-CM25</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1937,42 +1937,42 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.805.000-0</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>INDUSTRIA DE CAMAS Y TEXTILES LIMITADA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.404.809-1</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>47859981.85</v>
+        <v>15777.24</v>
       </c>
     </row>
     <row r="26">
@@ -2029,11 +2029,11 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>19175005.5</v>
+        <v>20929.69</v>
       </c>
     </row>
     <row r="27">
@@ -2090,11 +2090,11 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>5834136</v>
+        <v>6368.01</v>
       </c>
     </row>
     <row r="28">
@@ -2151,11 +2151,11 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>13231684.8</v>
+        <v>14442.5</v>
       </c>
     </row>
     <row r="29">
@@ -2212,11 +2212,11 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>8294300</v>
+        <v>9053.299999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2273,11 +2273,11 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>8103480.95</v>
+        <v>8845.02</v>
       </c>
     </row>
     <row r="31">
@@ -2334,17 +2334,17 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>5792848.6</v>
+        <v>6322.95</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>4629-819-CM25</t>
+          <t>883-221-CM25</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.104.000-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -2384,28 +2384,28 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>5880911.4</v>
+        <v>7615.88</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>948354-1689-CM25</t>
+          <t>1293138-370-CM25</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2425,17 +2425,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.513.003-6</t>
+          <t>61.608.200-0</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2445,28 +2445,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MUEBLES MELINA SPA</t>
+          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>77.472.821-K</t>
+          <t>77.749.210-1</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6932804</v>
+        <v>7508.76</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2178-421-CM25</t>
+          <t>5952-456-CM25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2486,48 +2486,48 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>INDUMAC LTDA.</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>83.732.700-8</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>12042008.65</v>
+        <v>34174.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1238177-156-CM25</t>
+          <t>2178-421-CM25</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2547,48 +2547,48 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cancelada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>65.165.009-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>ASOCIACION DE MUNICIPIOS METROPOLITANOS PARA LA SE</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>18729632.7</v>
+        <v>13143.96</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>883-221-CM25</t>
+          <t>948354-1689-CM25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,12 +2613,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.104.000-8</t>
+          <t>61.513.003-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE AERONAUTICA CIVIL</t>
+          <t>FONDO HOSPITAL DE LA DIRECCION DE PREVISION DE CARABINEROS DE CHILE</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2628,28 +2628,28 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>MUEBLES MELINA SPA</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>77.472.821-K</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>6977387.35</v>
+        <v>7567.22</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>5952-456-CM25</t>
+          <t>4629-819-CM25</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,48 +2669,48 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>INDUMAC LTDA.</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>83.732.700-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>31309235.14</v>
+        <v>6419.07</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1293138-370-CM25</t>
+          <t>1968-3290-CM25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2725,7 +2725,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2735,43 +2735,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.608.200-0</t>
+          <t>61.004.087-K</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE</t>
+          <t>Dirección Regional de Gendarmeria - Temuco</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE PRODUCTOS MEDICOS Y DEPORTIVOS PTM CHILE SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>77.749.210-1</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>6879247.2</v>
+        <v>9070.530000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2348-1647-CM25</t>
+          <t>591-7694-CM25</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2796,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>69.250.200-0</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>IDEA MARKET SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>76.148.288-2</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>5057500</v>
+        <v>44332.26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>633-1019-CM25</t>
+          <t>3232-757-CM25</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2852,48 +2852,48 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>LEFI SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>77.324.357-3</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>9840064.1</v>
+        <v>15523.1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>629373-422-CM25</t>
+          <t>633-1019-CM25</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2918,43 +2918,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>70.962.500-4</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>LEFI SPA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.324.357-3</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>6419000</v>
+        <v>10740.52</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>591-7694-CM25</t>
+          <t>2348-1647-CM25</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2979,43 +2979,43 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.250.200-0</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE PUNTA ARENAS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>IDEA MARKET SPA</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.148.288-2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>40615575.7</v>
+        <v>5520.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1968-3290-CM25</t>
+          <t>629373-422-CM25</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3040,43 +3040,43 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.004.087-K</t>
+          <t>70.962.500-4</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Temuco</t>
+          <t>CORP MUNICIPAL DE SAN MIGUEL</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>8310080.25</v>
+        <v>7006.4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>3232-757-CM25</t>
+          <t>1469-4213-CM25</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3096,48 +3096,48 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.625.647-3</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>14221690</v>
+        <v>48262.08</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1469-4213-CM25</t>
+          <t>1208102-83-CM25</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -3177,28 +3177,28 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>DISEÑO Y ARQUITECTURA SEBASTIAN SIEL BRUNET  E.I.R.L.</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.625.647-3</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>44215931.7</v>
+        <v>11137.31</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1208102-83-CM25</t>
+          <t>2176-623-CM25</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3218,48 +3218,48 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>10203590.4</v>
+        <v>8360.280000000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2176-623-CM25</t>
+          <t>1095439-18-CM25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,53 +3274,53 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025-12-17</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>72.222.000-5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>GOBIERNO REGIONAL DE AYSEN</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>7659382.08</v>
+        <v>17248.18</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1095439-18-CM25</t>
+          <t>5067-3410-CM25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3345,43 +3345,43 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>72.222.000-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE AYSEN</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>15802144.26</v>
+        <v>8316.879999999999</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>5067-3410-CM25</t>
+          <t>2832-5545-CM25</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,48 +3401,48 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>69.260.400-8</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>I MUNICIPALIDAD DE QUILLOTA</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>76.058.118-6</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>7619617.6</v>
+        <v>11089.19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2832-5545-CM25</t>
+          <t>4629-822-CM25</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3457,47 +3457,47 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>69.260.400-8</t>
+          <t>61.502.000-1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILLOTA</t>
+          <t>DIRECCION DEL TRABAJO</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA DE MUEBLES HP LIMITADA</t>
+          <t>MUEBLES TIMAUKEL LIMITADA</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>76.058.118-6</t>
+          <t>78.042.830-9</t>
         </is>
       </c>
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>10159506</v>
+        <v>14002.04</v>
       </c>
     </row>
     <row r="51">
@@ -3554,11 +3554,11 @@
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>10159317</v>
+        <v>11088.98</v>
       </c>
     </row>
     <row r="52">
@@ -3615,11 +3615,11 @@
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>58649298.75</v>
+        <v>64016.23</v>
       </c>
     </row>
     <row r="53">
@@ -3676,11 +3676,11 @@
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>12744347.84</v>
+        <v>13910.57</v>
       </c>
     </row>
     <row r="54">
@@ -3737,17 +3737,17 @@
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>26341500</v>
+        <v>28751.98</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>4629-822-CM25</t>
+          <t>1057448-675-CM25</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3772,43 +3772,43 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.502.000-1</t>
+          <t>61.606.100-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>DIRECCION DEL TRABAJO</t>
+          <t>SERVICIO DE SALUD IQUIQUE</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>MUEBLES TIMAUKEL LIMITADA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.042.830-9</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>12828146.45</v>
+        <v>46205.84</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1057448-675-CM25</t>
+          <t>1495199-3-CM25</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,7 +3823,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3833,12 +3833,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.606.100-3</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD IQUIQUE</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3848,28 +3848,28 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>42332080</v>
+        <v>19122</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2429-3187-CM25</t>
+          <t>1495202-3-SE25</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3889,17 +3889,17 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>69.020.300-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,28 +3909,32 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
+          <t>96.882.140-7</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Región Metropolitana de Santiago</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>52919804</v>
+        <v>16650.57</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1186229-388-CM25</t>
+          <t>1016414-189-CM25</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3955,12 +3959,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3970,28 +3974,28 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>76.007.474-8</t>
+          <t>76.710.414-6</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>71413209.90000001</v>
+        <v>7728.43</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1495202-3-SE25</t>
+          <t>2429-3187-CM25</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4011,17 +4015,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.020.300-6</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>I MUNICIPALIDAD DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,32 +4035,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>EVENTAIL SPA</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Región Metropolitana de Santiago</t>
-        </is>
-      </c>
+          <t>76.710.414-6</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>15254637</v>
+        <v>57762.43</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1385462-296-CM25</t>
+          <t>1495205-3-CM25</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4107,17 +4107,17 @@
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>33672173.78</v>
+        <v>15719.58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1495199-3-CM25</t>
+          <t>1186229-388-CM25</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4142,43 +4142,43 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA Y DISTRIBUIDORA LIBERONA S.A</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>76.007.474-8</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>17518865.14</v>
+        <v>77948.14999999999</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1495205-3-CM25</t>
+          <t>1495207-5-CM25</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4213,7 +4213,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4229,17 +4229,17 @@
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>14401693.88</v>
+        <v>17732.62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1495207-5-CM25</t>
+          <t>1385462-296-CM25</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>SERVICIO DE BIODIVERSIDAD Y ÁREAS PROTEGIDAS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4290,17 +4290,17 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>16245971.56</v>
+        <v>36753.47</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1016414-189-CM25</t>
+          <t>1495203-6-CM25</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4325,43 +4325,43 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>EVENTAIL SPA</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.710.414-6</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>7080500</v>
+        <v>13237.85</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1495203-6-CM25</t>
+          <t>1494998-5-CM25</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4412,17 +4412,17 @@
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>12128027.24</v>
+        <v>21179.18</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1494998-5-CM25</t>
+          <t>1495200-5-CM25</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4473,17 +4473,17 @@
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>19403576.64</v>
+        <v>19000.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1495200-5-CM25</t>
+          <t>2410-2656-CM25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4508,17 +4508,17 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>69.170.102-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4534,17 +4534,17 @@
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>17407729.22</v>
+        <v>9943.059999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2410-2656-CM25</t>
+          <t>2410-2655-CM25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4595,17 +4595,17 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>9109462.6</v>
+        <v>6323.08</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2410-2655-CM25</t>
+          <t>2410-2654-CM25</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4645,28 +4645,28 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>ENILDA TERESA FIGUEROA MELLADO</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>6.189.318-0</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>5792976</v>
+        <v>12734.25</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2410-2654-CM25</t>
+          <t>1495209-4-CM25</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4691,43 +4691,43 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>69.170.102-6</t>
+          <t>61.981.340-5</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANGELES AREA SALUD</t>
+          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ENILDA TERESA FIGUEROA MELLADO</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>6.189.318-0</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>11666648.8</v>
+        <v>13421.13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1495209-4-CM25</t>
+          <t>591-7711-CM25</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4742,53 +4742,53 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.981.340-5</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Servicio de Biodiversidad y Áreas Protegidas</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>MELMAN SPA</t>
+          <t>STATUS SPA</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.882.140-7</t>
+          <t>77.393.671-4</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>12295942.4</v>
+        <v>5484.98</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>591-7711-CM25</t>
+          <t>564162-1484-CM25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4808,17 +4808,17 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -4828,28 +4828,28 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>STATUS SPA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>77.393.671-4</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>5025132</v>
+        <v>27276.81</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>564162-1484-CM25</t>
+          <t>3453-679-CM25</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -4889,28 +4889,28 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>MUNDO LOCKERS SPA</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>76.580.205-9</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>24990000</v>
+        <v>37043.46</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3453-679-CM25</t>
+          <t>1563-93-CM25</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4935,43 +4935,43 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>61.603.000-0</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dirección de Educación, Doctrina e Historia de Carabineros</t>
+          <t>FONDO NACIONAL DE SALUD</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>MUNDO LOCKERS SPA</t>
+          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>76.580.205-9</t>
+          <t>11.372.911-2</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>33937848</v>
+        <v>9430.299999999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1563-93-CM25</t>
+          <t>3762-3515-CM25</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4986,53 +4986,53 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025-12-23</t>
+          <t>2025-12-24</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.603.000-0</t>
+          <t>69.200.900-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>FONDO NACIONAL DE SALUD</t>
+          <t>I MUNICIPALIDAD DE PAILLACO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>JOSÉ HERNÁN HENRÍQUEZ SEPÚLVEDA</t>
+          <t>COMERCIAL INNOVA PLACE SPA</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>11.372.911-2</t>
+          <t>77.599.784-2</t>
         </is>
       </c>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>8639693.76</v>
+        <v>69235.67999999999</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3762-3515-CM25</t>
+          <t>1208107-103-CM25</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5052,22 +5052,22 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>69.200.900-2</t>
+          <t>62.000.890-7</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAILLACO</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5083,17 +5083,17 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>63431165</v>
+        <v>17388.96</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1208107-103-CM25</t>
+          <t>1177296-589-CM25</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5123,38 +5123,38 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>COMERCIAL INNOVA PLACE SPA</t>
+          <t>IMPORTADORA FULLMUEBLES SPA</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>77.599.784-2</t>
+          <t>77.351.814-9</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>15931125</v>
+        <v>6091.82</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1177296-589-CM25</t>
+          <t>1210674-294-CM25</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA</t>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5194,28 +5194,28 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>IMPORTADORA FULLMUEBLES SPA</t>
+          <t>BODEGA STOCK SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>77.351.814-9</t>
+          <t>76.744.548-2</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>5581100</v>
+        <v>58739.57</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1186229-393-CM25</t>
+          <t>2178-432-CM25</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5240,43 +5240,43 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>MODUS Design Limitada</t>
+          <t>PROVEEDORES INTEGRALES PRISA S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>79.893.240-3</t>
+          <t>96.556.940-5</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>58867485.3</v>
+        <v>7673.64</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1210674-294-CM25</t>
+          <t>1186229-393-CM25</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>62.000.890-7</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -5316,28 +5316,28 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>BODEGA STOCK SPA</t>
+          <t>MODUS Design Limitada</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.744.548-2</t>
+          <t>79.893.240-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>53815019.8</v>
+        <v>64254.38</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2178-432-CM25</t>
+          <t>3608-767-CM25</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5352,53 +5352,53 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2025-12-24</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>PROVEEDORES INTEGRALES PRISA S A</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>96.556.940-5</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>7030304.95</v>
+        <v>21393.57</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3608-767-CM25</t>
+          <t>1057056-52-CM25</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5418,48 +5418,48 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>PLUSMEDICAL SPA</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>76.520.087-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>19599997.06</v>
+        <v>8141.35</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057056-52-CM25</t>
+          <t>316-978-CM25</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5474,47 +5474,47 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>69.061.500-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>PLUSMEDICAL SPA</t>
+          <t>Econosillas</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.520.087-3</t>
+          <t>76.067.326-9</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>7458801</v>
+        <v>12601.16</v>
       </c>
     </row>
     <row r="84">
@@ -5571,11 +5571,11 @@
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>16002173.1</v>
+        <v>17466.51</v>
       </c>
     </row>
     <row r="85">
@@ -5632,11 +5632,11 @@
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>5833574.65</v>
+        <v>6367.4</v>
       </c>
     </row>
     <row r="86">
@@ -5693,17 +5693,17 @@
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>57918612.4</v>
+        <v>63218.68</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>316-978-CM25</t>
+          <t>1186229-392-CM25</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5718,47 +5718,47 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2025-12-30</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>69.061.500-2</t>
+          <t>61.002.000-3</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VILLA ALEMANA</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Econosillas</t>
+          <t>CHILESEATING</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.067.326-9</t>
+          <t>76.675.854-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>11544714.45</v>
+        <v>49009.87</v>
       </c>
     </row>
     <row r="88">
@@ -5815,11 +5815,11 @@
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>13042281</v>
+        <v>14235.76</v>
       </c>
     </row>
     <row r="89">
@@ -5876,17 +5876,17 @@
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>17573920</v>
+        <v>19182.09</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1186229-392-CM25</t>
+          <t>1057858-26-CM25</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5911,12 +5911,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.002.000-3</t>
+          <t>61.608.600-6</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
+          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -5926,83 +5926,22 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>CHILESEATING</t>
+          <t>MELMAN SPA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>76.675.854-1</t>
+          <t>96.882.140-7</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>44901032.4</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>1057858-26-CM25</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>2239-4-LR25</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>dic-2025</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Recepcion Conforme</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>61.608.600-6</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD METROPOLITANO CENTRAL</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>MELMAN SPA</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>96.882.140-7</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="n">
-        <v>8329310.08</v>
+        <v>9091.52</v>
       </c>
     </row>
   </sheetData>
